--- a/template/PR439-Daily-Work-Report-TEMPLATE.xlsx
+++ b/template/PR439-Daily-Work-Report-TEMPLATE.xlsx
@@ -2092,8 +2092,7 @@
         <v>46</v>
       </c>
       <c r="Q9" s="10">
-        <f>Q5-Q7</f>
-        <v>-46164</v>
+        <f>Q5-Q7+1</f>
       </c>
       <c r="S9"/>
       <c r="T9"/>
